--- a/app/etl/Orçamento.xlsx
+++ b/app/etl/Orçamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C003C800-6113-4709-98C6-3AA35B93D270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D1F1C7-1F92-4CA2-BE5F-C82D7273E04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{41714D36-5029-4B1C-A721-B587E9DEF73C}"/>
   </bookViews>
@@ -1130,9 +1130,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1149,6 +1149,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="singleAccounting"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1175,16 +1183,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1192,7 +1201,26 @@
   </cellStyles>
   <dxfs count="29">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1211,7 +1239,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1230,7 +1261,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1249,7 +1283,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1268,7 +1305,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1287,7 +1327,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1306,7 +1349,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1325,7 +1371,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1344,7 +1393,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1363,7 +1415,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1382,7 +1437,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1401,26 +1459,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1435,40 +1477,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1484,25 +1493,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47CBA2B2-F8B0-4099-9593-0AF59AAE4E92}" name="Tabela1" displayName="Tabela1" ref="A1:P1237" totalsRowCount="1" headerRowDxfId="0">
-  <autoFilter ref="A1:P1236" xr:uid="{47CBA2B2-F8B0-4099-9593-0AF59AAE4E92}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47CBA2B2-F8B0-4099-9593-0AF59AAE4E92}" name="Tabela1" displayName="Tabela1" ref="A1:P1237" totalsRowCount="1" headerRowDxfId="28">
   <tableColumns count="16">
-    <tableColumn id="19" xr3:uid="{48E0D215-9294-4CF3-8A37-967C4F72F501}" name="Produto" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{2F09BD5A-1D17-4243-8517-E979F96857E4}" name="Descrição" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{14B67C36-3436-4597-87BB-2933BD90189E}" name="Categoria" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{68B21E57-9B1E-409B-8BC0-8CC24E8048AB}" name="Segmento" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{D3DC6722-AFAB-460C-A6E8-83CDCFEC3BDA}" name="jan" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="12" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{887032EB-93DB-4AC3-9C38-62D37A65AAB6}" name="fev" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="11" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{4D52475E-D2BB-4E24-8C57-AFBBFCD1F9CC}" name="mar" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="10" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{C46DD520-1F3B-4801-B5B0-0F5B6444F705}" name="abr" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="9" dataCellStyle="Moeda"/>
-    <tableColumn id="10" xr3:uid="{1BC4A16B-7B83-4CCF-B5B0-16BF26E2C935}" name="mai" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="8" dataCellStyle="Moeda"/>
-    <tableColumn id="11" xr3:uid="{2156971C-C88E-491D-A449-15656CCE7D54}" name="jun" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="7" dataCellStyle="Moeda"/>
-    <tableColumn id="12" xr3:uid="{E0DD6884-9E47-4EBF-88B5-92E79AFE86A4}" name="jul" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="6" dataCellStyle="Moeda"/>
-    <tableColumn id="13" xr3:uid="{04545893-8976-435F-BD79-B999ED32A51D}" name="ago" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="5" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{B007BD9E-E41C-4B17-A40E-3B16A17E90CC}" name="set" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="4" dataCellStyle="Moeda"/>
-    <tableColumn id="15" xr3:uid="{118801EF-D8EA-46B5-9F0C-1C7CFB8AD7E2}" name="out" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="3" dataCellStyle="Moeda"/>
-    <tableColumn id="16" xr3:uid="{C9E08778-11A4-4665-B396-07413332AA14}" name="nov" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="2" dataCellStyle="Moeda"/>
-    <tableColumn id="17" xr3:uid="{0DE17B75-C3E5-4A3E-8714-04520C713390}" name="dez" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="1" dataCellStyle="Moeda"/>
+    <tableColumn id="19" xr3:uid="{48E0D215-9294-4CF3-8A37-967C4F72F501}" name="Produto" dataDxfId="27"/>
+    <tableColumn id="20" xr3:uid="{2F09BD5A-1D17-4243-8517-E979F96857E4}" name="Descrição" dataDxfId="26"/>
+    <tableColumn id="21" xr3:uid="{14B67C36-3436-4597-87BB-2933BD90189E}" name="Categoria" dataDxfId="25"/>
+    <tableColumn id="22" xr3:uid="{68B21E57-9B1E-409B-8BC0-8CC24E8048AB}" name="Segmento" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{D3DC6722-AFAB-460C-A6E8-83CDCFEC3BDA}" name="jan" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{887032EB-93DB-4AC3-9C38-62D37A65AAB6}" name="fev" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{4D52475E-D2BB-4E24-8C57-AFBBFCD1F9CC}" name="mar" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{C46DD520-1F3B-4801-B5B0-0F5B6444F705}" name="abr" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Moeda"/>
+    <tableColumn id="10" xr3:uid="{1BC4A16B-7B83-4CCF-B5B0-16BF26E2C935}" name="mai" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Moeda"/>
+    <tableColumn id="11" xr3:uid="{2156971C-C88E-491D-A449-15656CCE7D54}" name="jun" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Moeda"/>
+    <tableColumn id="12" xr3:uid="{E0DD6884-9E47-4EBF-88B5-92E79AFE86A4}" name="jul" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Moeda"/>
+    <tableColumn id="13" xr3:uid="{04545893-8976-435F-BD79-B999ED32A51D}" name="ago" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{B007BD9E-E41C-4B17-A40E-3B16A17E90CC}" name="set" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Moeda"/>
+    <tableColumn id="15" xr3:uid="{118801EF-D8EA-46B5-9F0C-1C7CFB8AD7E2}" name="out" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Moeda"/>
+    <tableColumn id="16" xr3:uid="{C9E08778-11A4-4665-B396-07413332AA14}" name="nov" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Moeda"/>
+    <tableColumn id="17" xr3:uid="{0DE17B75-C3E5-4A3E-8714-04520C713390}" name="dez" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4167,7 +4175,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>410060104</v>
+        <v>410060199</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
@@ -4217,7 +4225,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>410060204</v>
+        <v>410060299</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
@@ -4267,7 +4275,7 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>410060304</v>
+        <v>410060399</v>
       </c>
       <c r="B50" t="s">
         <v>59</v>
@@ -4317,7 +4325,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>410060404</v>
+        <v>410060499</v>
       </c>
       <c r="B51" t="s">
         <v>60</v>
@@ -4367,7 +4375,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>410066304</v>
+        <v>410066399</v>
       </c>
       <c r="B52" t="s">
         <v>61</v>
@@ -11567,7 +11575,7 @@
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>410060104</v>
+        <v>410060199</v>
       </c>
       <c r="B196" t="s">
         <v>57</v>
@@ -11617,7 +11625,7 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>410060204</v>
+        <v>410060299</v>
       </c>
       <c r="B197" t="s">
         <v>58</v>
@@ -11667,7 +11675,7 @@
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>410060304</v>
+        <v>410060399</v>
       </c>
       <c r="B198" t="s">
         <v>59</v>
@@ -11717,7 +11725,7 @@
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>410060404</v>
+        <v>410060499</v>
       </c>
       <c r="B199" t="s">
         <v>60</v>
@@ -11767,7 +11775,7 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>410066304</v>
+        <v>410066399</v>
       </c>
       <c r="B200" t="s">
         <v>61</v>
@@ -18967,7 +18975,7 @@
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A344">
-        <v>410060104</v>
+        <v>410060199</v>
       </c>
       <c r="B344" t="s">
         <v>57</v>
@@ -19017,7 +19025,7 @@
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A345">
-        <v>410060204</v>
+        <v>410060299</v>
       </c>
       <c r="B345" t="s">
         <v>58</v>
@@ -19067,7 +19075,7 @@
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A346">
-        <v>410060304</v>
+        <v>410060399</v>
       </c>
       <c r="B346" t="s">
         <v>59</v>
@@ -19117,7 +19125,7 @@
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A347">
-        <v>410060404</v>
+        <v>410060499</v>
       </c>
       <c r="B347" t="s">
         <v>60</v>
@@ -19167,7 +19175,7 @@
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A348">
-        <v>410066304</v>
+        <v>410066399</v>
       </c>
       <c r="B348" t="s">
         <v>61</v>
@@ -26367,7 +26375,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A492">
-        <v>410060104</v>
+        <v>410060199</v>
       </c>
       <c r="B492" t="s">
         <v>57</v>
@@ -26417,7 +26425,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A493">
-        <v>410060204</v>
+        <v>410060299</v>
       </c>
       <c r="B493" t="s">
         <v>58</v>
@@ -26467,7 +26475,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A494">
-        <v>410060304</v>
+        <v>410060399</v>
       </c>
       <c r="B494" t="s">
         <v>59</v>
@@ -26517,7 +26525,7 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A495">
-        <v>410060404</v>
+        <v>410060499</v>
       </c>
       <c r="B495" t="s">
         <v>60</v>
@@ -26567,7 +26575,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A496">
-        <v>410066304</v>
+        <v>410066399</v>
       </c>
       <c r="B496" t="s">
         <v>61</v>
@@ -33767,7 +33775,7 @@
     </row>
     <row r="640" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A640">
-        <v>410060104</v>
+        <v>410060199</v>
       </c>
       <c r="B640" t="s">
         <v>57</v>
@@ -33817,7 +33825,7 @@
     </row>
     <row r="641" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A641">
-        <v>410060204</v>
+        <v>410060299</v>
       </c>
       <c r="B641" t="s">
         <v>58</v>
@@ -33867,7 +33875,7 @@
     </row>
     <row r="642" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A642">
-        <v>410060304</v>
+        <v>410060399</v>
       </c>
       <c r="B642" t="s">
         <v>59</v>
@@ -33917,7 +33925,7 @@
     </row>
     <row r="643" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A643">
-        <v>410060404</v>
+        <v>410060499</v>
       </c>
       <c r="B643" t="s">
         <v>60</v>
@@ -33967,7 +33975,7 @@
     </row>
     <row r="644" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A644">
-        <v>410066304</v>
+        <v>410066399</v>
       </c>
       <c r="B644" t="s">
         <v>61</v>
@@ -45081,7 +45089,7 @@
     </row>
     <row r="867" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A867">
-        <v>410060104</v>
+        <v>410060199</v>
       </c>
       <c r="B867" t="s">
         <v>57</v>
@@ -45131,7 +45139,7 @@
     </row>
     <row r="868" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A868">
-        <v>410060204</v>
+        <v>410060299</v>
       </c>
       <c r="B868" t="s">
         <v>58</v>
@@ -45181,7 +45189,7 @@
     </row>
     <row r="869" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A869">
-        <v>410060304</v>
+        <v>410060399</v>
       </c>
       <c r="B869" t="s">
         <v>59</v>
@@ -45231,7 +45239,7 @@
     </row>
     <row r="870" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A870">
-        <v>410060404</v>
+        <v>410060499</v>
       </c>
       <c r="B870" t="s">
         <v>60</v>
@@ -45281,7 +45289,7 @@
     </row>
     <row r="871" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A871">
-        <v>410066304</v>
+        <v>410066399</v>
       </c>
       <c r="B871" t="s">
         <v>61</v>
@@ -51781,7 +51789,7 @@
     </row>
     <row r="1001" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1001">
-        <v>410060104</v>
+        <v>410060199</v>
       </c>
       <c r="B1001" t="s">
         <v>57</v>
@@ -51831,7 +51839,7 @@
     </row>
     <row r="1002" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1002">
-        <v>410060204</v>
+        <v>410060299</v>
       </c>
       <c r="B1002" t="s">
         <v>58</v>
@@ -51881,7 +51889,7 @@
     </row>
     <row r="1003" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1003">
-        <v>410060304</v>
+        <v>410060399</v>
       </c>
       <c r="B1003" t="s">
         <v>59</v>
@@ -51931,7 +51939,7 @@
     </row>
     <row r="1004" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1004">
-        <v>410060404</v>
+        <v>410060499</v>
       </c>
       <c r="B1004" t="s">
         <v>60</v>
@@ -51981,7 +51989,7 @@
     </row>
     <row r="1005" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1005">
-        <v>410066304</v>
+        <v>410066399</v>
       </c>
       <c r="B1005" t="s">
         <v>61</v>
@@ -63279,7 +63287,7 @@
         <v>1096.797835859375</v>
       </c>
     </row>
-    <row r="1231" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1231" spans="1:16" ht="16.2" x14ac:dyDescent="0.45">
       <c r="A1231">
         <v>410100105</v>
       </c>
@@ -63319,7 +63327,7 @@
       <c r="M1231" s="1">
         <v>1692.6518770858397</v>
       </c>
-      <c r="N1231" s="1">
+      <c r="N1231" s="5">
         <v>1692.6518770858397</v>
       </c>
       <c r="O1231" s="1">
